--- a/zib2017-2020/zib_versions.xlsx
+++ b/zib2017-2020/zib_versions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lindamook/Documents/GitHub/zibtranslate/zib2017-2020/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/wouter_zanen_nictiz_nl/Documents/Documenten/GitHub/Zibtranslate/zib2017-2020/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388C1A51-1026-0E49-B90D-AE64119FA45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="1180" windowWidth="34900" windowHeight="16940" xr2:uid="{6A031DF4-A5D7-7D41-A8E4-057E405138E6}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{6A031DF4-A5D7-7D41-A8E4-057E405138E6}"/>
   </bookViews>
   <sheets>
     <sheet name="table_info_zibs" sheetId="8" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2079,7 +2079,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -4973,7 +4973,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BCBA0AD-29B9-5C4B-9C96-C22F11902962}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BCBA0AD-29B9-5C4B-9C96-C22F11902962}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A329" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -6379,7 +6379,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -6696,17 +6696,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190018DB-705B-1C49-8BBE-D7735C134696}">
   <dimension ref="A1:J116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="2" width="41.33203125" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.5" customWidth="1"/>
-    <col min="5" max="5" width="67.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="71.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="5" max="5" width="67.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="71.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>277</v>
       </c>
@@ -6742,7 +6742,7 @@
       <c r="E2" s="13"/>
       <c r="F2" s="14"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>383</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="E3" s="16"/>
       <c r="F3" s="17"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>506</v>
       </c>
@@ -6774,7 +6774,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="14"/>
     </row>
-    <row r="5" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>524</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>298</v>
       </c>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="F6" s="14"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>527</v>
       </c>
@@ -6828,7 +6828,7 @@
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>249</v>
       </c>
@@ -6844,7 +6844,7 @@
       <c r="E8" s="13"/>
       <c r="F8" s="14"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>420</v>
       </c>
@@ -6860,7 +6860,7 @@
       <c r="E9" s="16"/>
       <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:6" ht="112" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>202</v>
       </c>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="F10" s="14"/>
     </row>
-    <row r="11" spans="1:6" ht="125" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="125.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>368</v>
       </c>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="F11" s="17"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>304</v>
       </c>
@@ -6912,7 +6912,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>374</v>
       </c>
@@ -6928,7 +6928,7 @@
       <c r="E13" s="16"/>
       <c r="F13" s="17"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>212</v>
       </c>
@@ -6944,7 +6944,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>408</v>
       </c>
@@ -6960,7 +6960,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="17"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>274</v>
       </c>
@@ -6976,7 +6976,7 @@
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>365</v>
       </c>
@@ -6992,7 +6992,7 @@
       <c r="E17" s="16"/>
       <c r="F17" s="17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>521</v>
       </c>
@@ -7008,7 +7008,7 @@
       <c r="E18" s="13"/>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>252</v>
       </c>
@@ -7024,7 +7024,7 @@
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>237</v>
       </c>
@@ -7040,7 +7040,7 @@
       <c r="E20" s="13"/>
       <c r="F20" s="14"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>323</v>
       </c>
@@ -7056,7 +7056,7 @@
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>386</v>
       </c>
@@ -7072,7 +7072,7 @@
       <c r="E22" s="13"/>
       <c r="F22" s="14"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>392</v>
       </c>
@@ -7088,7 +7088,7 @@
       <c r="E23" s="16"/>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>411</v>
       </c>
@@ -7104,7 +7104,7 @@
       <c r="E24" s="13"/>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
         <v>356</v>
       </c>
@@ -7120,7 +7120,7 @@
       <c r="E25" s="16"/>
       <c r="F25" s="17"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>353</v>
       </c>
@@ -7136,7 +7136,7 @@
       <c r="E26" s="13"/>
       <c r="F26" s="14"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>509</v>
       </c>
@@ -7152,7 +7152,7 @@
       <c r="E27" s="16"/>
       <c r="F27" s="17"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>476</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
         <v>551</v>
       </c>
@@ -7184,7 +7184,7 @@
       <c r="E29" s="16"/>
       <c r="F29" s="17"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>240</v>
       </c>
@@ -7200,7 +7200,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="14"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>417</v>
       </c>
@@ -7216,7 +7216,7 @@
       <c r="E31" s="16"/>
       <c r="F31" s="17"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>414</v>
       </c>
@@ -7232,7 +7232,7 @@
       <c r="E32" s="13"/>
       <c r="F32" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>426</v>
       </c>
@@ -7248,7 +7248,7 @@
       <c r="E33" s="16"/>
       <c r="F33" s="17"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>537</v>
       </c>
@@ -7264,7 +7264,7 @@
       <c r="E34" s="13"/>
       <c r="F34" s="14"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>488</v>
       </c>
@@ -7280,7 +7280,7 @@
       <c r="E35" s="16"/>
       <c r="F35" s="17"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>497</v>
       </c>
@@ -7296,7 +7296,7 @@
       <c r="E36" s="13"/>
       <c r="F36" s="14"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>286</v>
       </c>
@@ -7312,7 +7312,7 @@
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>271</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="E38" s="13"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>362</v>
       </c>
@@ -7344,7 +7344,7 @@
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>395</v>
       </c>
@@ -7360,7 +7360,7 @@
       <c r="E40" s="13"/>
       <c r="F40" s="14"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>218</v>
       </c>
@@ -7376,7 +7376,7 @@
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>292</v>
       </c>
@@ -7392,7 +7392,7 @@
       <c r="E42" s="13"/>
       <c r="F42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>512</v>
       </c>
@@ -7408,7 +7408,7 @@
       <c r="E43" s="16"/>
       <c r="F43" s="17"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>231</v>
       </c>
@@ -7424,7 +7424,7 @@
       <c r="E44" s="13"/>
       <c r="F44" s="14"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>262</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="E45" s="16"/>
       <c r="F45" s="17"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>280</v>
       </c>
@@ -7456,7 +7456,7 @@
       <c r="E46" s="13"/>
       <c r="F46" s="14"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
         <v>548</v>
       </c>
@@ -7472,7 +7472,7 @@
       <c r="E47" s="16"/>
       <c r="F47" s="17"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>534</v>
       </c>
@@ -7488,7 +7488,7 @@
       <c r="E48" s="13"/>
       <c r="F48" s="14"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>540</v>
       </c>
@@ -7504,7 +7504,7 @@
       <c r="E49" s="16"/>
       <c r="F49" s="17"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>556</v>
       </c>
@@ -7520,7 +7520,7 @@
       <c r="E50" s="13"/>
       <c r="F50" s="14"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
         <v>215</v>
       </c>
@@ -7536,7 +7536,7 @@
       <c r="E51" s="16"/>
       <c r="F51" s="17"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>438</v>
       </c>
@@ -7552,7 +7552,7 @@
       <c r="E52" s="13"/>
       <c r="F52" s="14"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
         <v>460</v>
       </c>
@@ -7568,7 +7568,7 @@
       <c r="E53" s="16"/>
       <c r="F53" s="17"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>380</v>
       </c>
@@ -7584,7 +7584,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
         <v>515</v>
       </c>
@@ -7600,7 +7600,7 @@
       <c r="E55" s="16"/>
       <c r="F55" s="17"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>234</v>
       </c>
@@ -7616,7 +7616,7 @@
       <c r="E56" s="13"/>
       <c r="F56" s="14"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
         <v>447</v>
       </c>
@@ -7632,7 +7632,7 @@
       <c r="E57" s="16"/>
       <c r="F57" s="17"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>479</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
     </row>
-    <row r="59" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A59" s="15" t="s">
         <v>329</v>
       </c>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F59" s="17"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>350</v>
       </c>
@@ -7682,7 +7682,7 @@
       <c r="E60" s="13"/>
       <c r="F60" s="14"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="15" t="s">
         <v>207</v>
       </c>
@@ -7698,7 +7698,7 @@
       <c r="E61" s="16"/>
       <c r="F61" s="17"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>289</v>
       </c>
@@ -7714,7 +7714,7 @@
       <c r="E62" s="13"/>
       <c r="F62" s="14"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
         <v>283</v>
       </c>
@@ -7730,7 +7730,7 @@
       <c r="E63" s="16"/>
       <c r="F63" s="17"/>
     </row>
-    <row r="64" spans="1:6" ht="126" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>472</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
         <v>243</v>
       </c>
@@ -7766,7 +7766,7 @@
       <c r="E65" s="16"/>
       <c r="F65" s="17"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>441</v>
       </c>
@@ -7782,7 +7782,7 @@
       <c r="E66" s="13"/>
       <c r="F66" s="14"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="15" t="s">
         <v>435</v>
       </c>
@@ -7798,7 +7798,7 @@
       <c r="E67" s="16"/>
       <c r="F67" s="17"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
         <v>463</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="E68" s="13"/>
       <c r="F68" s="14"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="15" t="s">
         <v>221</v>
       </c>
@@ -7830,7 +7830,7 @@
       <c r="E69" s="16"/>
       <c r="F69" s="17"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>224</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="E70" s="13"/>
       <c r="F70" s="14"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="15" t="s">
         <v>432</v>
       </c>
@@ -7862,7 +7862,7 @@
       <c r="E71" s="16"/>
       <c r="F71" s="17"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
         <v>485</v>
       </c>
@@ -7878,7 +7878,7 @@
       <c r="E72" s="13"/>
       <c r="F72" s="14"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="15" t="s">
         <v>503</v>
       </c>
@@ -7894,7 +7894,7 @@
       <c r="E73" s="16"/>
       <c r="F73" s="17"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>295</v>
       </c>
@@ -7910,7 +7910,7 @@
       <c r="E74" s="13"/>
       <c r="F74" s="14"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="15" t="s">
         <v>377</v>
       </c>
@@ -7926,7 +7926,7 @@
       <c r="E75" s="16"/>
       <c r="F75" s="17"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
         <v>554</v>
       </c>
@@ -7942,7 +7942,7 @@
       <c r="E76" s="13"/>
       <c r="F76" s="14"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="15" t="s">
         <v>301</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="E77" s="16"/>
       <c r="F77" s="17"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
         <v>228</v>
       </c>
@@ -7974,7 +7974,7 @@
       <c r="E78" s="13"/>
       <c r="F78" s="14"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="15" t="s">
         <v>469</v>
       </c>
@@ -7990,7 +7990,7 @@
       <c r="E79" s="16"/>
       <c r="F79" s="17"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
         <v>466</v>
       </c>
@@ -8006,7 +8006,7 @@
       <c r="E80" s="13"/>
       <c r="F80" s="14"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="15" t="s">
         <v>405</v>
       </c>
@@ -8022,7 +8022,7 @@
       <c r="E81" s="16"/>
       <c r="F81" s="17"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="12" t="s">
         <v>423</v>
       </c>
@@ -8038,7 +8038,7 @@
       <c r="E82" s="13"/>
       <c r="F82" s="14"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="15" t="s">
         <v>450</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="E83" s="16"/>
       <c r="F83" s="17"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="12" t="s">
         <v>453</v>
       </c>
@@ -8070,7 +8070,7 @@
       <c r="E84" s="13"/>
       <c r="F84" s="14"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="15" t="s">
         <v>456</v>
       </c>
@@ -8086,7 +8086,7 @@
       <c r="E85" s="16"/>
       <c r="F85" s="17"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>402</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="E86" s="13"/>
       <c r="F86" s="14"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="15" t="s">
         <v>399</v>
       </c>
@@ -8118,7 +8118,7 @@
       <c r="E87" s="16"/>
       <c r="F87" s="17"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="12" t="s">
         <v>314</v>
       </c>
@@ -8134,7 +8134,7 @@
       <c r="E88" s="13"/>
       <c r="F88" s="14"/>
     </row>
-    <row r="89" spans="1:6" ht="126" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
         <v>311</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>530</v>
       </c>
@@ -8170,7 +8170,7 @@
       <c r="E90" s="13"/>
       <c r="F90" s="14"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="15" t="s">
         <v>246</v>
       </c>
@@ -8186,7 +8186,7 @@
       <c r="E91" s="16"/>
       <c r="F91" s="17"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="12" t="s">
         <v>482</v>
       </c>
@@ -8202,7 +8202,7 @@
       <c r="E92" s="13"/>
       <c r="F92" s="14"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="15" t="s">
         <v>444</v>
       </c>
@@ -8218,7 +8218,7 @@
       <c r="E93" s="16"/>
       <c r="F93" s="17"/>
     </row>
-    <row r="94" spans="1:6" ht="56" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>317</v>
       </c>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F94" s="14"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="15" t="s">
         <v>494</v>
       </c>
@@ -8252,7 +8252,7 @@
       <c r="E95" s="16"/>
       <c r="F95" s="17"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="12" t="s">
         <v>359</v>
       </c>
@@ -8268,7 +8268,7 @@
       <c r="E96" s="13"/>
       <c r="F96" s="14"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="15" t="s">
         <v>518</v>
       </c>
@@ -8284,7 +8284,7 @@
       <c r="E97" s="16"/>
       <c r="F97" s="17"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="12" t="s">
         <v>347</v>
       </c>
@@ -8300,7 +8300,7 @@
       <c r="E98" s="13"/>
       <c r="F98" s="14"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
         <v>341</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="E99" s="16"/>
       <c r="F99" s="17"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="12" t="s">
         <v>338</v>
       </c>
@@ -8332,7 +8332,7 @@
       <c r="E100" s="13"/>
       <c r="F100" s="14"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
         <v>491</v>
       </c>
@@ -8348,7 +8348,7 @@
       <c r="E101" s="16"/>
       <c r="F101" s="17"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="12" t="s">
         <v>389</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="E102" s="13"/>
       <c r="F102" s="14"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="15" t="s">
         <v>371</v>
       </c>
@@ -8380,7 +8380,7 @@
       <c r="E103" s="16"/>
       <c r="F103" s="17"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="12" t="s">
         <v>255</v>
       </c>
@@ -8396,7 +8396,7 @@
       <c r="E104" s="13"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
         <v>326</v>
       </c>
@@ -8412,7 +8412,7 @@
       <c r="E105" s="16"/>
       <c r="F105" s="17"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="12" t="s">
         <v>268</v>
       </c>
@@ -8428,7 +8428,7 @@
       <c r="E106" s="13"/>
       <c r="F106" s="14"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
         <v>265</v>
       </c>
@@ -8444,7 +8444,7 @@
       <c r="E107" s="16"/>
       <c r="F107" s="17"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="12" t="s">
         <v>307</v>
       </c>
@@ -8460,7 +8460,7 @@
       <c r="E108" s="13"/>
       <c r="F108" s="14"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
         <v>429</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="E109" s="16"/>
       <c r="F109" s="17"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="12" t="s">
         <v>259</v>
       </c>
@@ -8492,7 +8492,7 @@
       <c r="E110" s="13"/>
       <c r="F110" s="14"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
         <v>320</v>
       </c>
@@ -8508,7 +8508,7 @@
       <c r="E111" s="16"/>
       <c r="F111" s="17"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="12" t="s">
         <v>332</v>
       </c>
@@ -8524,7 +8524,7 @@
       <c r="E112" s="13"/>
       <c r="F112" s="14"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
         <v>335</v>
       </c>
@@ -8540,7 +8540,7 @@
       <c r="E113" s="16"/>
       <c r="F113" s="17"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
         <v>344</v>
       </c>
@@ -8556,7 +8556,7 @@
       <c r="E114" s="8"/>
       <c r="F114" s="18"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
         <v>500</v>
       </c>
@@ -8574,7 +8574,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
         <v>543</v>
       </c>
@@ -8607,1643 +8607,1643 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCFD827-7ADE-CC42-A664-40C1A9F4F2E3}">
   <dimension ref="A3:A329"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="68.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="4" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" s="4" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" s="3" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A247" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A248" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A249" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A253" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A255" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" s="3" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
         <v>602</v>
       </c>
@@ -10256,18 +10256,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD818E27-D014-A348-BCE0-0E812E70AA74}">
   <dimension ref="A1:J211"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
-    <col min="4" max="5" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>383</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>383</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>506</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>506</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>524</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>524</v>
       </c>
@@ -10519,7 +10519,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>298</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>527</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>527</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>389</v>
       </c>
@@ -10629,7 +10629,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>249</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>249</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>420</v>
       </c>
@@ -10710,7 +10710,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>420</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>202</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>368</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>371</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>304</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>304</v>
       </c>
@@ -10881,7 +10881,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -10910,7 +10910,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>212</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>212</v>
       </c>
@@ -10991,7 +10991,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>408</v>
       </c>
@@ -11017,7 +11017,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>408</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>274</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>274</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>365</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>365</v>
       </c>
@@ -11156,7 +11156,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>521</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>521</v>
       </c>
@@ -11211,7 +11211,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>252</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>252</v>
       </c>
@@ -11266,7 +11266,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>237</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>237</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>323</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>323</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>386</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>386</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>392</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>392</v>
       </c>
@@ -11486,7 +11486,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>411</v>
       </c>
@@ -11515,7 +11515,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>411</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>255</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>356</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>356</v>
       </c>
@@ -11625,7 +11625,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>353</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>353</v>
       </c>
@@ -11680,7 +11680,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>509</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>509</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>476</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>476</v>
       </c>
@@ -11790,7 +11790,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>551</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>551</v>
       </c>
@@ -11845,7 +11845,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>240</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>240</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>417</v>
       </c>
@@ -11926,7 +11926,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>417</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>414</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>414</v>
       </c>
@@ -12010,7 +12010,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>426</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>426</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>537</v>
       </c>
@@ -12091,7 +12091,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>537</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>488</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>488</v>
       </c>
@@ -12175,7 +12175,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>497</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>497</v>
       </c>
@@ -12230,7 +12230,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>286</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>286</v>
       </c>
@@ -12285,7 +12285,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>271</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>271</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>362</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>362</v>
       </c>
@@ -12395,7 +12395,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>395</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>395</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>218</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>218</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>500</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>292</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>292</v>
       </c>
@@ -12589,7 +12589,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>512</v>
       </c>
@@ -12615,7 +12615,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>512</v>
       </c>
@@ -12644,7 +12644,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>231</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>231</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>262</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>280</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>280</v>
       </c>
@@ -12809,7 +12809,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>548</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>548</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>543</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>534</v>
       </c>
@@ -12919,7 +12919,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>534</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>540</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>540</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>556</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>556</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>215</v>
       </c>
@@ -13084,7 +13084,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>215</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>438</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>438</v>
       </c>
@@ -13168,7 +13168,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>460</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>460</v>
       </c>
@@ -13223,7 +13223,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>380</v>
       </c>
@@ -13249,7 +13249,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>380</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>515</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>515</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>234</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>234</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>447</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>447</v>
       </c>
@@ -13443,7 +13443,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>479</v>
       </c>
@@ -13469,7 +13469,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>479</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>329</v>
       </c>
@@ -13527,7 +13527,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>350</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>350</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>207</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>207</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>326</v>
       </c>
@@ -13663,7 +13663,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>268</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>289</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>289</v>
       </c>
@@ -13747,7 +13747,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>283</v>
       </c>
@@ -13773,7 +13773,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>283</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>472</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>472</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>265</v>
       </c>
@@ -13886,7 +13886,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>243</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>243</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>441</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>441</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>435</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>435</v>
       </c>
@@ -14051,7 +14051,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>463</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>463</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>307</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>221</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>221</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>224</v>
       </c>
@@ -14216,7 +14216,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>224</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>432</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>432</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>485</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>485</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>503</v>
       </c>
@@ -14381,7 +14381,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>503</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>295</v>
       </c>
@@ -14436,7 +14436,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>295</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>377</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>377</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>429</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>554</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>554</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>301</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>301</v>
       </c>
@@ -14659,7 +14659,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>228</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>228</v>
       </c>
@@ -14714,7 +14714,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>469</v>
       </c>
@@ -14743,7 +14743,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>469</v>
       </c>
@@ -14769,7 +14769,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>466</v>
       </c>
@@ -14798,7 +14798,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>466</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>405</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>405</v>
       </c>
@@ -14879,7 +14879,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>423</v>
       </c>
@@ -14908,7 +14908,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>423</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>450</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>450</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>453</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>453</v>
       </c>
@@ -15044,7 +15044,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>456</v>
       </c>
@@ -15073,7 +15073,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>456</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>402</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>402</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>399</v>
       </c>
@@ -15183,7 +15183,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>399</v>
       </c>
@@ -15209,7 +15209,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>314</v>
       </c>
@@ -15235,7 +15235,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>314</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>311</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>311</v>
       </c>
@@ -15319,7 +15319,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>530</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>530</v>
       </c>
@@ -15374,7 +15374,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>259</v>
       </c>
@@ -15403,7 +15403,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>246</v>
       </c>
@@ -15432,7 +15432,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>246</v>
       </c>
@@ -15458,7 +15458,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>482</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>482</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>444</v>
       </c>
@@ -15539,7 +15539,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>444</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>320</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>317</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>494</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>494</v>
       </c>
@@ -15681,7 +15681,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>359</v>
       </c>
@@ -15707,7 +15707,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>359</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>518</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>518</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>347</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>347</v>
       </c>
@@ -15846,7 +15846,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>341</v>
       </c>
@@ -15872,7 +15872,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>341</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>332</v>
       </c>
@@ -15930,7 +15930,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>335</v>
       </c>
@@ -15959,7 +15959,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>344</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>338</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>338</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>491</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>491</v>
       </c>
@@ -16112,14 +16112,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF75645-D2C8-D54C-989B-0700AFD1F77D}">
   <dimension ref="A1:E116"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" customWidth="1"/>
+    <col min="1" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16136,7 +16136,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>202</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>207</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>212</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>215</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>218</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -16223,7 +16223,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>224</v>
       </c>
@@ -16237,7 +16237,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>231</v>
       </c>
@@ -16265,7 +16265,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>234</v>
       </c>
@@ -16279,7 +16279,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>237</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>240</v>
       </c>
@@ -16307,7 +16307,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>243</v>
       </c>
@@ -16321,7 +16321,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>246</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>249</v>
       </c>
@@ -16349,7 +16349,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>252</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>259</v>
       </c>
@@ -16391,7 +16391,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>262</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>265</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>268</v>
       </c>
@@ -16433,7 +16433,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>271</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>274</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>277</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>280</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>283</v>
       </c>
@@ -16503,7 +16503,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -16517,7 +16517,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>289</v>
       </c>
@@ -16531,7 +16531,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>292</v>
       </c>
@@ -16545,7 +16545,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>295</v>
       </c>
@@ -16559,7 +16559,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>298</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>301</v>
       </c>
@@ -16587,7 +16587,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>304</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -16629,7 +16629,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>314</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>317</v>
       </c>
@@ -16657,7 +16657,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>320</v>
       </c>
@@ -16671,7 +16671,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>323</v>
       </c>
@@ -16685,7 +16685,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>326</v>
       </c>
@@ -16699,7 +16699,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>332</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>335</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -16755,7 +16755,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>344</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>347</v>
       </c>
@@ -16797,7 +16797,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>350</v>
       </c>
@@ -16811,7 +16811,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>353</v>
       </c>
@@ -16825,7 +16825,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>356</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>359</v>
       </c>
@@ -16853,7 +16853,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>365</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>368</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>371</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>374</v>
       </c>
@@ -16923,7 +16923,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>377</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>380</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>383</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>386</v>
       </c>
@@ -16979,7 +16979,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>389</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>392</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>395</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>399</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>402</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>405</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>408</v>
       </c>
@@ -17077,7 +17077,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>411</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>414</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>417</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>420</v>
       </c>
@@ -17133,7 +17133,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>423</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>426</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>429</v>
       </c>
@@ -17175,7 +17175,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>432</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>435</v>
       </c>
@@ -17203,7 +17203,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>438</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>441</v>
       </c>
@@ -17231,7 +17231,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>444</v>
       </c>
@@ -17245,7 +17245,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>447</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>450</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>453</v>
       </c>
@@ -17287,7 +17287,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>456</v>
       </c>
@@ -17301,7 +17301,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>460</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>463</v>
       </c>
@@ -17329,7 +17329,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>466</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>469</v>
       </c>
@@ -17357,7 +17357,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>472</v>
       </c>
@@ -17371,7 +17371,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>476</v>
       </c>
@@ -17385,7 +17385,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>479</v>
       </c>
@@ -17399,7 +17399,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>482</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>485</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>488</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -17455,7 +17455,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>494</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>497</v>
       </c>
@@ -17483,7 +17483,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>500</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>503</v>
       </c>
@@ -17511,7 +17511,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>506</v>
       </c>
@@ -17525,7 +17525,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>509</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>512</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>515</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>518</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>521</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>524</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>527</v>
       </c>
@@ -17623,7 +17623,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>530</v>
       </c>
@@ -17637,7 +17637,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>534</v>
       </c>
@@ -17651,7 +17651,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>537</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>540</v>
       </c>
@@ -17679,7 +17679,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>543</v>
       </c>
@@ -17693,7 +17693,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>556</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>548</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>551</v>
       </c>
@@ -17735,7 +17735,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>554</v>
       </c>
